--- a/product_selector_out/STM32C55x-562.xlsx
+++ b/product_selector_out/STM32C55x-562.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM36"/>
+  <dimension ref="A1:BN36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.86328125" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c562ce.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c562ce.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c562ce.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c562ce.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c562ce.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -8181,6 +8293,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -8835,6 +8957,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -9162,12 +9289,17 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -9188,16 +9320,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -9210,6 +9340,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -9229,7 +9360,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -9271,7 +9404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM36"/>
+  <dimension ref="A1:BN36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9339,6 +9472,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9672,6 +9806,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -9767,6 +9906,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -10089,7 +10229,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10416,7 +10561,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10743,7 +10893,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11070,7 +11225,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11397,7 +11557,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11724,7 +11889,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12051,7 +12221,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12378,7 +12553,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12705,7 +12885,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13032,7 +13217,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13359,7 +13549,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13686,7 +13881,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14013,7 +14213,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14340,7 +14545,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14667,7 +14877,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14994,7 +15209,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15321,7 +15541,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15648,7 +15873,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15975,7 +16205,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16302,7 +16537,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16629,7 +16869,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16956,7 +17201,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17283,7 +17533,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17610,7 +17865,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17937,7 +18197,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17945,8 +18210,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
